--- a/Result/profitability/3702.xlsx
+++ b/Result/profitability/3702.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM82"/>
+  <dimension ref="A1:AM83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.44375</v>
+        <v>1.93125</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0725</v>
+        <v>4.220000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="N3" t="n">
-        <v>4.47125</v>
+        <v>4.575</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.33125</v>
+        <v>1.83</v>
       </c>
       <c r="N4" t="n">
-        <v>4.83</v>
+        <v>4.91875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>1.24375</v>
+        <v>1.7525</v>
       </c>
       <c r="N5" t="n">
-        <v>5.10125</v>
+        <v>5.1775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>1.19</v>
+        <v>1.59375</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4175</v>
+        <v>5.4675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0625</v>
+        <v>1.49125</v>
       </c>
       <c r="N7" t="n">
-        <v>5.655</v>
+        <v>5.67625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01625</v>
+        <v>1.24375</v>
       </c>
       <c r="N8" t="n">
-        <v>5.85125</v>
+        <v>5.84375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -10826,6 +10826,133 @@
       </c>
       <c r="AM82" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>456211</v>
+      </c>
+      <c r="D83" t="n">
+        <v>436014</v>
+      </c>
+      <c r="E83" t="n">
+        <v>20197</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="G83" t="n">
+        <v>11954</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>-658</v>
+      </c>
+      <c r="J83" t="n">
+        <v>11296</v>
+      </c>
+      <c r="K83" t="n">
+        <v>8620</v>
+      </c>
+      <c r="L83" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0.5515151515151517</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>-0.0600000000000005</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>-0.01336302895322949</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>3.876190476190476</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0.6099999999999999</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0.1596858638743455</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK83" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
